--- a/пример тест-кейса.xlsx
+++ b/пример тест-кейса.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\3-МД-4 ПИ\Беленова Анастасия\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1BBED10-FAA7-446E-B0E9-9DD37CD94A26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E68A80A-CB88-4310-ABE9-B4DE4E8362C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
